--- a/Resources/Advisory Board.xlsx
+++ b/Resources/Advisory Board.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/samataluintel/Documents/WISE Website/Resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE97CC0-9FC5-2F4E-AE9A-7AFFCDC72AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E3719ED-5FEE-5148-86EB-D1395E41F5AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17960" activeTab="3" xr2:uid="{913FFF3F-0973-774E-8715-7A357E0A590C}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="1" r:id="rId1"/>
@@ -19,28 +19,12 @@
     <sheet name="2022" sheetId="4" r:id="rId4"/>
     <sheet name="2021" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="47">
   <si>
     <t>Name</t>
   </si>
@@ -54,13 +38,133 @@
     <t>Sub-committee</t>
   </si>
   <si>
+    <t>Aleeza Rana</t>
+  </si>
+  <si>
+    <t>Carly Daniel</t>
+  </si>
+  <si>
+    <t>Connie Chen</t>
+  </si>
+  <si>
+    <t>Faith Jung</t>
+  </si>
+  <si>
+    <t>Julia Steele</t>
+  </si>
+  <si>
+    <t>Karina Osma Perez</t>
+  </si>
+  <si>
+    <t>Katherine Vincent</t>
+  </si>
+  <si>
+    <t>Kyla Richardson</t>
+  </si>
+  <si>
+    <t>Mckinley Lowden</t>
+  </si>
+  <si>
+    <t>Nicole Sherman</t>
+  </si>
+  <si>
+    <t>Remington Reaves</t>
+  </si>
+  <si>
+    <t>Sophie Perrigin</t>
+  </si>
+  <si>
+    <t>Taylor Adams</t>
+  </si>
+  <si>
+    <t>Addison Kiteley</t>
+  </si>
+  <si>
+    <t>Alua Bekbossynova</t>
+  </si>
+  <si>
+    <t>Clare Tjaden</t>
+  </si>
+  <si>
+    <t>Ellie Joyce</t>
+  </si>
+  <si>
+    <t>Gabrielle Martis</t>
+  </si>
+  <si>
+    <t>Katherine Thomas</t>
+  </si>
+  <si>
+    <t>Madison Simpson</t>
+  </si>
+  <si>
+    <t>Natalie Tews</t>
+  </si>
+  <si>
+    <t>Randilyn Gomme</t>
+  </si>
+  <si>
+    <t>Shaylee Graves</t>
+  </si>
+  <si>
+    <t>Shelby Gabrielson</t>
+  </si>
+  <si>
+    <t>Skylar Rotter</t>
+  </si>
+  <si>
+    <t>Abby Garretson</t>
+  </si>
+  <si>
+    <t>Addie Miles</t>
+  </si>
+  <si>
+    <t>Amy Hernandez</t>
+  </si>
+  <si>
+    <t>Breanna Schneider</t>
+  </si>
+  <si>
+    <t>Caitlin Curmode</t>
+  </si>
+  <si>
+    <t>Claire Hudson</t>
+  </si>
+  <si>
+    <t>Elah Spence</t>
+  </si>
+  <si>
+    <t>Lauren Casey</t>
+  </si>
+  <si>
+    <t>Maddie Dorish</t>
+  </si>
+  <si>
+    <t>Madison Farrens</t>
+  </si>
+  <si>
+    <t>Olivia Kropp</t>
+  </si>
+  <si>
+    <t>Sally Wysong</t>
+  </si>
+  <si>
+    <t>Tiziana Ortega</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>Director</t>
+  </si>
+  <si>
     <t>Chair</t>
   </si>
   <si>
-    <t>Director</t>
-  </si>
-  <si>
-    <t>Contact</t>
+    <t>l</t>
+  </si>
+  <si>
+    <t>Alaina Suggs</t>
   </si>
 </sst>
 </file>
@@ -431,7 +535,363 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E302BCF2-6537-2B4E-BAB8-1235EF7CDB1C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="29.6640625" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="29.6640625" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="29.6640625" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="29.6640625" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -457,175 +917,12 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C2" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A70E1AD5-334F-D443-8E95-77AA4E19F37B}">
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="29.6640625" customWidth="1"/>
-    <col min="2" max="2" width="26.83203125" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EE492BC-153B-C64E-8E52-D975C7468B68}">
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="29.6640625" customWidth="1"/>
-    <col min="2" max="2" width="26.83203125" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08208130-0312-6240-8F4D-8F9D5829E456}">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="29.6640625" customWidth="1"/>
-    <col min="2" max="2" width="26.83203125" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D95415B-1934-F943-A374-9ECBBCA2B00A}">
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="29.6640625" customWidth="1"/>
-    <col min="2" max="2" width="26.83203125" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C3" t="s">
-        <v>4</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/Resources/Advisory Board.xlsx
+++ b/Resources/Advisory Board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/samataluintel/Documents/WISE Website/Resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E3719ED-5FEE-5148-86EB-D1395E41F5AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35A5C7A6-7338-924F-979A-018940795323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="15080" windowHeight="18900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="1" r:id="rId1"/>
